--- a/output/2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore di utensili manuali ed elettrici professionali (cordless, compressori, smerigliatrici, accessori). Sede: Partizanska cesta 15, 2390 Ravne na Koroškem. Fondata nel 1989. Email verificata tramite ricerca è 'trgovina@interdiskont.si' (esiste anche 'narocila@interdiskont.si' per ordini).</t>
+          <t>Rivenditore di utensili manuali ed elettrici professionali (cordless, compressori, smerigliatrici, accessori). Sede: Partizanska cesta 15, 2390 Ravne na Koroškem. Fondata nel 1989. Email verificata tramite ricerca è 'trgovina@interdiskont.si' (esiste anche 'narocila@interdiskont.si' per ordini). [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grande punto vendita della catena Merkur (bricolage/ferramenta/casa-giardino-officina), Ronkova ulica 35, 2380 Slovenj Gradec. Rivenditore generalista con reparto utensili, non specialista B2B dedicato.</t>
+          <t>Grande punto vendita della catena Merkur (bricolage/ferramenta/casa-giardino-officina), Ronkova ulica 35, 2380 Slovenj Gradec. Rivenditore generalista con reparto utensili, non specialista B2B dedicato. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
